--- a/file/De-mi ตัวอย่างลงรายชื่อ.xlsx
+++ b/file/De-mi ตัวอย่างลงรายชื่อ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ratsapanphuksaritanon/Desktop/Tone/Dao/doc/AppBolt/demi-plus-web-v2/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D2B5044-AEA4-D643-92C8-39B8AF31328D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D830C9E1-EB99-B44F-BCDD-32C61D75BBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="23260" windowHeight="12460" xr2:uid="{493625A2-FE23-49F0-8D72-420B791986D6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="69">
   <si>
     <t>เลขบัตรประชาชน</t>
   </si>
@@ -102,18 +102,12 @@
     <t>รหัสไปรษณีย์</t>
   </si>
   <si>
-    <t>ชื่อผู้ติดต่อ(ญาติ)</t>
-  </si>
-  <si>
     <t>เบอร์โทร</t>
   </si>
   <si>
     <t>ความสัมพันธ์</t>
   </si>
   <si>
-    <t>ชื่อผู้ดูแล (อสม.)</t>
-  </si>
-  <si>
     <t>นายบุญเพ็ง</t>
   </si>
   <si>
@@ -162,21 +156,9 @@
     <t>ไม่มี</t>
   </si>
   <si>
-    <t>รพ.สต.</t>
-  </si>
-  <si>
-    <t>รพ.สต.บ้านฟ้าใส</t>
-  </si>
-  <si>
-    <t>รพ.สต.ร่มไทร</t>
-  </si>
-  <si>
     <t>ร่มไทร</t>
   </si>
   <si>
-    <t>รพ.เมตตาธรรม</t>
-  </si>
-  <si>
     <t>สมอเทพ</t>
   </si>
   <si>
@@ -250,6 +232,15 @@
   </si>
   <si>
     <t>นายศักดา ประกาศ</t>
+  </si>
+  <si>
+    <t>รพ.เพชรบูรณ์</t>
+  </si>
+  <si>
+    <t>ผู้ติดต่อ</t>
+  </si>
+  <si>
+    <t>โค้ช</t>
   </si>
 </sst>
 </file>
@@ -608,11 +599,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{304D6687-A08E-4522-B130-AE76F7E06B63}">
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.5" style="3" customWidth="1"/>
+    <col min="2" max="2" width="23" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="19.1640625" customWidth="1"/>
     <col min="5" max="5" width="20.5" customWidth="1"/>
@@ -621,20 +612,20 @@
     <col min="11" max="11" width="34.5" customWidth="1"/>
     <col min="12" max="12" width="14.5" customWidth="1"/>
     <col min="13" max="13" width="23.33203125" customWidth="1"/>
-    <col min="14" max="15" width="22.5" customWidth="1"/>
-    <col min="19" max="19" width="13.1640625" customWidth="1"/>
-    <col min="20" max="20" width="15.5" customWidth="1"/>
-    <col min="21" max="21" width="16.5" customWidth="1"/>
-    <col min="22" max="22" width="15.1640625" customWidth="1"/>
-    <col min="23" max="23" width="14.5" customWidth="1"/>
-    <col min="24" max="24" width="18.5" customWidth="1"/>
-    <col min="25" max="25" width="24.5" customWidth="1"/>
-    <col min="26" max="26" width="23.1640625" customWidth="1"/>
-    <col min="27" max="27" width="16.1640625" customWidth="1"/>
-    <col min="28" max="28" width="18.83203125" customWidth="1"/>
+    <col min="14" max="14" width="22.5" customWidth="1"/>
+    <col min="18" max="18" width="13.1640625" customWidth="1"/>
+    <col min="19" max="19" width="15.5" customWidth="1"/>
+    <col min="20" max="20" width="16.5" customWidth="1"/>
+    <col min="21" max="21" width="15.1640625" customWidth="1"/>
+    <col min="22" max="22" width="14.5" customWidth="1"/>
+    <col min="23" max="23" width="18.5" customWidth="1"/>
+    <col min="24" max="24" width="24.5" customWidth="1"/>
+    <col min="25" max="25" width="23.1640625" customWidth="1"/>
+    <col min="26" max="26" width="16.1640625" customWidth="1"/>
+    <col min="27" max="27" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -654,7 +645,7 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H1" t="s">
         <v>6</v>
@@ -678,34 +669,34 @@
         <v>12</v>
       </c>
       <c r="O1" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="P1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X1" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="Y1" t="s">
         <v>22</v>
@@ -714,33 +705,30 @@
         <v>23</v>
       </c>
       <c r="AA1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>5555555555555</v>
+        <v>1666666666666</v>
       </c>
       <c r="B2" s="3">
         <v>236683</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E2">
         <v>45688899</v>
       </c>
       <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="H2">
         <v>80</v>
@@ -752,7 +740,7 @@
         <v>100</v>
       </c>
       <c r="K2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L2">
         <v>140</v>
@@ -761,69 +749,66 @@
         <v>6.8</v>
       </c>
       <c r="N2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" t="s">
-        <v>43</v>
+        <v>66</v>
+      </c>
+      <c r="O2">
+        <v>54</v>
       </c>
       <c r="P2">
-        <v>54</v>
-      </c>
-      <c r="Q2">
         <v>12</v>
       </c>
+      <c r="Q2" t="s">
+        <v>42</v>
+      </c>
       <c r="R2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="S2" t="s">
         <v>50</v>
       </c>
       <c r="T2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="U2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="V2" t="s">
-        <v>59</v>
-      </c>
-      <c r="W2" t="s">
-        <v>58</v>
-      </c>
-      <c r="X2">
+        <v>52</v>
+      </c>
+      <c r="W2">
         <v>99000</v>
       </c>
-      <c r="Y2" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z2">
+      <c r="X2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y2">
         <v>857741248</v>
       </c>
+      <c r="Z2" t="s">
+        <v>60</v>
+      </c>
       <c r="AA2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>1234567890000</v>
+        <v>1555555555555</v>
       </c>
       <c r="B3" s="3">
         <v>235359</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E3">
         <v>95562310</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G3">
         <v>956321476</v>
@@ -838,78 +823,75 @@
         <v>95</v>
       </c>
       <c r="K3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L3">
         <v>105</v>
       </c>
       <c r="M3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N3" t="s">
-        <v>46</v>
-      </c>
-      <c r="O3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O3">
+        <v>85</v>
+      </c>
+      <c r="P3">
+        <v>5</v>
+      </c>
+      <c r="Q3" t="s">
         <v>43</v>
       </c>
-      <c r="P3">
-        <v>85</v>
-      </c>
-      <c r="Q3">
-        <v>5</v>
-      </c>
       <c r="R3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" t="s">
         <v>49</v>
       </c>
-      <c r="S3" t="s">
-        <v>41</v>
-      </c>
       <c r="T3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="U3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="V3" t="s">
-        <v>59</v>
-      </c>
-      <c r="W3" t="s">
-        <v>48</v>
-      </c>
-      <c r="X3">
+        <v>42</v>
+      </c>
+      <c r="W3">
         <v>99000</v>
       </c>
-      <c r="Y3" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z3">
+      <c r="X3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y3">
         <v>946524875</v>
       </c>
+      <c r="Z3" t="s">
+        <v>61</v>
+      </c>
       <c r="AA3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>9873216541234</v>
+        <v>1444444444444</v>
       </c>
       <c r="B4" s="3">
         <v>230464</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E4">
         <v>74125836</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G4">
         <v>625458792</v>
@@ -924,7 +906,7 @@
         <v>95</v>
       </c>
       <c r="K4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L4">
         <v>130</v>
@@ -933,69 +915,66 @@
         <v>6.9</v>
       </c>
       <c r="N4" t="s">
-        <v>46</v>
-      </c>
-      <c r="O4" t="s">
-        <v>44</v>
+        <v>66</v>
+      </c>
+      <c r="O4">
+        <v>12</v>
       </c>
       <c r="P4">
-        <v>12</v>
-      </c>
-      <c r="Q4">
         <v>4</v>
       </c>
+      <c r="Q4" t="s">
+        <v>40</v>
+      </c>
       <c r="R4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="S4" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="T4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="U4" t="s">
+        <v>53</v>
+      </c>
+      <c r="V4" t="s">
+        <v>40</v>
+      </c>
+      <c r="W4">
+        <v>99000</v>
+      </c>
+      <c r="X4" t="s">
         <v>57</v>
       </c>
-      <c r="V4" t="s">
-        <v>59</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4">
-        <v>99000</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z4">
+      <c r="Y4">
         <v>681245568</v>
       </c>
+      <c r="Z4" t="s">
+        <v>61</v>
+      </c>
       <c r="AA4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>1478523691472</v>
+        <v>1222222222222</v>
       </c>
       <c r="B5" s="3">
         <v>223020</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E5">
         <v>59123458</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G5">
         <v>921247854</v>
@@ -1010,7 +989,7 @@
         <v>110</v>
       </c>
       <c r="K5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L5">
         <v>120</v>
@@ -1019,69 +998,66 @@
         <v>8</v>
       </c>
       <c r="N5" t="s">
-        <v>46</v>
-      </c>
-      <c r="O5" t="s">
-        <v>46</v>
+        <v>66</v>
+      </c>
+      <c r="O5">
+        <v>136</v>
       </c>
       <c r="P5">
-        <v>136</v>
-      </c>
-      <c r="Q5">
         <v>8</v>
       </c>
+      <c r="Q5" t="s">
+        <v>41</v>
+      </c>
       <c r="R5" t="s">
+        <v>45</v>
+      </c>
+      <c r="S5" t="s">
         <v>47</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>51</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>53</v>
       </c>
-      <c r="U5" t="s">
-        <v>57</v>
-      </c>
       <c r="V5" t="s">
-        <v>59</v>
-      </c>
-      <c r="W5" t="s">
-        <v>60</v>
-      </c>
-      <c r="X5">
+        <v>54</v>
+      </c>
+      <c r="W5">
         <v>99000</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="X5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y5">
+        <v>968745523</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA5" t="s">
         <v>64</v>
       </c>
-      <c r="Z5">
-        <v>968745523</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>70</v>
-      </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>3698741236987</v>
+        <v>1333333333333</v>
       </c>
       <c r="B6" s="3">
         <v>219792</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E6">
         <v>14753069</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G6">
         <v>812443615</v>
@@ -1096,7 +1072,7 @@
         <v>103</v>
       </c>
       <c r="K6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L6">
         <v>119</v>
@@ -1105,49 +1081,46 @@
         <v>7.32</v>
       </c>
       <c r="N6" t="s">
+        <v>66</v>
+      </c>
+      <c r="O6">
+        <v>98</v>
+      </c>
+      <c r="P6">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>40</v>
+      </c>
+      <c r="R6" t="s">
         <v>46</v>
       </c>
-      <c r="O6" t="s">
-        <v>44</v>
-      </c>
-      <c r="P6">
-        <v>98</v>
-      </c>
-      <c r="Q6">
-        <v>2</v>
-      </c>
-      <c r="R6" t="s">
-        <v>45</v>
-      </c>
       <c r="S6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="T6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="V6" t="s">
+        <v>40</v>
+      </c>
+      <c r="W6">
+        <v>99000</v>
+      </c>
+      <c r="X6" t="s">
         <v>59</v>
       </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6">
-        <v>99000</v>
-      </c>
-      <c r="Y6" t="s">
+      <c r="Y6">
+        <v>845631247</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA6" t="s">
         <v>65</v>
-      </c>
-      <c r="Z6">
-        <v>845631247</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/file/De-mi ตัวอย่างลงรายชื่อ.xlsx
+++ b/file/De-mi ตัวอย่างลงรายชื่อ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ratsapanphuksaritanon/Desktop/Tone/Dao/doc/AppBolt/demi-plus-web-v2/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D830C9E1-EB99-B44F-BCDD-32C61D75BBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0CE8D78-870A-C24B-B92D-1706E4D39590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="23260" windowHeight="12460" xr2:uid="{493625A2-FE23-49F0-8D72-420B791986D6}"/>
   </bookViews>
@@ -280,11 +280,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -710,9 +711,9 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>1666666666666</v>
-      </c>
-      <c r="B2" s="3">
+        <v>3101400386644</v>
+      </c>
+      <c r="B2" s="4">
         <v>236683</v>
       </c>
       <c r="C2" t="s">
@@ -795,7 +796,7 @@
       <c r="A3" s="2">
         <v>1555555555555</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>235359</v>
       </c>
       <c r="C3" t="s">
